--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2134,7 +2134,7 @@
       <c r="C30" s="4" t="n">
         <v>4.64</v>
       </c>
-      <c r="D30" s="4" t="inlineStr"/>
+      <c r="D30" s="4" t="n"/>
       <c r="E30" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
@@ -2162,18 +2162,162 @@
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L30" s="3" t="inlineStr"/>
-      <c r="M30" s="4" t="inlineStr"/>
-      <c r="N30" s="4" t="inlineStr"/>
-      <c r="O30" s="4" t="inlineStr"/>
+      <c r="L30" s="3" t="n"/>
+      <c r="M30" s="4" t="n"/>
+      <c r="N30" s="4" t="n"/>
+      <c r="O30" s="4" t="n"/>
       <c r="P30" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>1.7385</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>2.8815</v>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>未进入加大买入区间</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>4.49</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>23.03</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>6.12</t>
+        </is>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁公开页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="D32" s="4" t="inlineStr"/>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>1.7376</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>2.9324</v>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>未进入加大买入区间</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>4.54</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>26.17</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>6.12</t>
+        </is>
+      </c>
+      <c r="P32" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁公开页面</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P30"/>
+  <autoFilter ref="A1:P32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2258,7 +2258,7 @@
       <c r="C32" s="4" t="n">
         <v>4.67</v>
       </c>
-      <c r="D32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="n"/>
       <c r="E32" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
@@ -2316,8 +2316,224 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>1.7398</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>2.950200000000001</v>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>未进入加大买入区间</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>4.53</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>25.76</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t>6.12</t>
+        </is>
+      </c>
+      <c r="P33" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁公开页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>1.7442</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>2.9358</v>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K34" s="7" t="inlineStr">
+        <is>
+          <t>未进入加大买入区间</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>4.45</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>18.78</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>6.12</t>
+        </is>
+      </c>
+      <c r="P34" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁公开页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="D35" s="4" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>1.7402</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>2.8398</v>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>未进入加大买入区间</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>4.42</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>15.75</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>6.12</t>
+        </is>
+      </c>
+      <c r="P35" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁公开页面</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P32"/>
+  <autoFilter ref="A1:P35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2474,7 +2474,7 @@
       <c r="C35" s="4" t="n">
         <v>4.58</v>
       </c>
-      <c r="D35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="n"/>
       <c r="E35" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2532,8 +2532,60 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="D36" s="4" t="inlineStr"/>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>1.7406</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>2.7794</v>
+      </c>
+      <c r="H36" s="6" t="inlineStr"/>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K36" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr"/>
+      <c r="M36" s="4" t="inlineStr"/>
+      <c r="N36" s="4" t="inlineStr"/>
+      <c r="O36" s="4" t="inlineStr"/>
+      <c r="P36" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P35"/>
+  <autoFilter ref="A1:P36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:P37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2546,7 +2546,7 @@
       <c r="C36" s="4" t="n">
         <v>4.52</v>
       </c>
-      <c r="D36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="n"/>
       <c r="E36" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
@@ -2574,18 +2574,90 @@
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L36" s="3" t="inlineStr"/>
-      <c r="M36" s="4" t="inlineStr"/>
-      <c r="N36" s="4" t="inlineStr"/>
-      <c r="O36" s="4" t="inlineStr"/>
+      <c r="L36" s="3" t="n"/>
+      <c r="M36" s="4" t="n"/>
+      <c r="N36" s="4" t="n"/>
+      <c r="O36" s="4" t="n"/>
       <c r="P36" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="D37" s="4" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>1.7437</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>2.8263</v>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>未进入加大买入区间</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>4.45</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>18.87</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>6.12</t>
+        </is>
+      </c>
+      <c r="P37" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁公开页面</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P36"/>
+  <autoFilter ref="A1:P37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P37"/>
+  <dimension ref="A1:P38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2598,7 +2598,7 @@
       <c r="C37" s="4" t="n">
         <v>4.57</v>
       </c>
-      <c r="D37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="n"/>
       <c r="E37" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
@@ -2656,8 +2656,80 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D38" s="4" t="inlineStr"/>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>1.7404</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>2.859599999999999</v>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>未进入加大买入区间</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>4.38</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>12.26</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>6.12</t>
+        </is>
+      </c>
+      <c r="P38" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁公开页面</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P37"/>
+  <autoFilter ref="A1:P38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P38"/>
+  <dimension ref="A1:P39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2670,7 +2670,7 @@
       <c r="C38" s="4" t="n">
         <v>4.6</v>
       </c>
-      <c r="D38" s="4" t="inlineStr"/>
+      <c r="D38" s="4" t="n"/>
       <c r="E38" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
@@ -2728,8 +2728,60 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="D39" s="4" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>1.7453</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>2.7147</v>
+      </c>
+      <c r="H39" s="6" t="inlineStr"/>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr"/>
+      <c r="M39" s="4" t="inlineStr"/>
+      <c r="N39" s="4" t="inlineStr"/>
+      <c r="O39" s="4" t="inlineStr"/>
+      <c r="P39" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P38"/>
+  <autoFilter ref="A1:P39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P39"/>
+  <dimension ref="A1:P40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2742,7 +2742,7 @@
       <c r="C39" s="4" t="n">
         <v>4.46</v>
       </c>
-      <c r="D39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="n"/>
       <c r="E39" s="3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2770,18 +2770,70 @@
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L39" s="3" t="inlineStr"/>
-      <c r="M39" s="4" t="inlineStr"/>
-      <c r="N39" s="4" t="inlineStr"/>
-      <c r="O39" s="4" t="inlineStr"/>
+      <c r="L39" s="3" t="n"/>
+      <c r="M39" s="4" t="n"/>
+      <c r="N39" s="4" t="n"/>
+      <c r="O39" s="4" t="n"/>
       <c r="P39" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="D40" s="4" t="inlineStr"/>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>1.7297</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>2.7303</v>
+      </c>
+      <c r="H40" s="6" t="inlineStr"/>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr"/>
+      <c r="M40" s="4" t="inlineStr"/>
+      <c r="N40" s="4" t="inlineStr"/>
+      <c r="O40" s="4" t="inlineStr"/>
+      <c r="P40" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P39"/>
+  <autoFilter ref="A1:P40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2794,7 +2794,7 @@
       <c r="C40" s="4" t="n">
         <v>4.46</v>
       </c>
-      <c r="D40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="n"/>
       <c r="E40" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
@@ -2822,18 +2822,90 @@
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L40" s="3" t="inlineStr"/>
-      <c r="M40" s="4" t="inlineStr"/>
-      <c r="N40" s="4" t="inlineStr"/>
-      <c r="O40" s="4" t="inlineStr"/>
+      <c r="L40" s="3" t="n"/>
+      <c r="M40" s="4" t="n"/>
+      <c r="N40" s="4" t="n"/>
+      <c r="O40" s="4" t="n"/>
       <c r="P40" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="D41" s="4" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>1.7325</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>2.6775</v>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>未进入加大买入区间</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>4.23</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>4.96</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>6.12</t>
+        </is>
+      </c>
+      <c r="P41" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁公开页面</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P40"/>
+  <autoFilter ref="A1:P41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:P42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2846,7 +2846,7 @@
       <c r="C41" s="4" t="n">
         <v>4.41</v>
       </c>
-      <c r="D41" s="4" t="inlineStr"/>
+      <c r="D41" s="4" t="n"/>
       <c r="E41" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -2904,8 +2904,60 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D42" s="4" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>1.7282</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>2.7718</v>
+      </c>
+      <c r="H42" s="6" t="inlineStr"/>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K42" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr"/>
+      <c r="M42" s="4" t="inlineStr"/>
+      <c r="N42" s="4" t="inlineStr"/>
+      <c r="O42" s="4" t="inlineStr"/>
+      <c r="P42" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P41"/>
+  <autoFilter ref="A1:P42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P42"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -609,7 +609,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AKShare股息率2(%)</t>
+          <t>指数股息率口径(%)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       <c r="C42" s="4" t="n">
         <v>4.5</v>
       </c>
-      <c r="D42" s="4" t="inlineStr"/>
+      <c r="D42" s="4" t="n"/>
       <c r="E42" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
@@ -2946,18 +2946,142 @@
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L42" s="3" t="inlineStr"/>
-      <c r="M42" s="4" t="inlineStr"/>
-      <c r="N42" s="4" t="inlineStr"/>
-      <c r="O42" s="4" t="inlineStr"/>
+      <c r="L42" s="3" t="n"/>
+      <c r="M42" s="4" t="n"/>
+      <c r="N42" s="4" t="n"/>
+      <c r="O42" s="4" t="n"/>
       <c r="P42" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>1.7337</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>2.7363</v>
+      </c>
+      <c r="H43" s="6" t="inlineStr"/>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="n"/>
+      <c r="M43" s="4" t="n"/>
+      <c r="N43" s="4" t="n"/>
+      <c r="O43" s="4" t="n"/>
+      <c r="P43" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="D44" s="4" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>1.7351</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>2.7349</v>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K44" s="7" t="inlineStr">
+        <is>
+          <t>未进入加大买入区间</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>4.18</t>
+        </is>
+      </c>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="O44" s="4" t="inlineStr">
+        <is>
+          <t>6.11</t>
+        </is>
+      </c>
+      <c r="P44" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁公开页面</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P42"/>
+  <autoFilter ref="A1:P44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:P46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3022,7 +3022,7 @@
       <c r="C44" s="4" t="n">
         <v>4.47</v>
       </c>
-      <c r="D44" s="4" t="inlineStr"/>
+      <c r="D44" s="4" t="n"/>
       <c r="E44" s="3" t="inlineStr">
         <is>
           <t>2026-07-28</t>
@@ -3080,8 +3080,152 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>1.7329</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>2.6671</v>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>未进入加大买入区间</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="inlineStr">
+        <is>
+          <t>4.18</t>
+        </is>
+      </c>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="O45" s="4" t="inlineStr">
+        <is>
+          <t>6.11</t>
+        </is>
+      </c>
+      <c r="P45" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁公开页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="D46" s="4" t="inlineStr"/>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>1.7196</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>2.640400000000001</v>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K46" s="7" t="inlineStr">
+        <is>
+          <t>未进入加大买入区间</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="O46" s="4" t="inlineStr">
+        <is>
+          <t>6.11</t>
+        </is>
+      </c>
+      <c r="P46" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁公开页面</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P44"/>
+  <autoFilter ref="A1:P46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P46"/>
+  <dimension ref="A1:P48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3166,7 +3166,7 @@
       <c r="C46" s="4" t="n">
         <v>4.36</v>
       </c>
-      <c r="D46" s="4" t="inlineStr"/>
+      <c r="D46" s="4" t="n"/>
       <c r="E46" s="3" t="inlineStr">
         <is>
           <t>2026-07-30</t>
@@ -3224,8 +3224,112 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="D47" s="4" t="n"/>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>1.7141</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>2.4359</v>
+      </c>
+      <c r="H47" s="6" t="inlineStr"/>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="n"/>
+      <c r="M47" s="4" t="n"/>
+      <c r="N47" s="4" t="n"/>
+      <c r="O47" s="4" t="n"/>
+      <c r="P47" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="D48" s="4" t="inlineStr"/>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>1.7169</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>2.4431</v>
+      </c>
+      <c r="H48" s="6" t="inlineStr"/>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K48" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr"/>
+      <c r="M48" s="4" t="inlineStr"/>
+      <c r="N48" s="4" t="inlineStr"/>
+      <c r="O48" s="4" t="inlineStr"/>
+      <c r="P48" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P46"/>
+  <autoFilter ref="A1:P48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P48"/>
+  <dimension ref="A1:P50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3290,7 +3290,7 @@
       <c r="C48" s="4" t="n">
         <v>4.16</v>
       </c>
-      <c r="D48" s="4" t="inlineStr"/>
+      <c r="D48" s="4" t="n"/>
       <c r="E48" s="3" t="inlineStr">
         <is>
           <t>2026-08-03</t>
@@ -3318,18 +3318,162 @@
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L48" s="3" t="inlineStr"/>
-      <c r="M48" s="4" t="inlineStr"/>
-      <c r="N48" s="4" t="inlineStr"/>
-      <c r="O48" s="4" t="inlineStr"/>
+      <c r="L48" s="3" t="n"/>
+      <c r="M48" s="4" t="n"/>
+      <c r="N48" s="4" t="n"/>
+      <c r="O48" s="4" t="n"/>
       <c r="P48" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="D49" s="4" t="n"/>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>1.7126</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>2.5174</v>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>未进入加大买入区间</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="M49" s="4" t="inlineStr">
+        <is>
+          <t>4.28</t>
+        </is>
+      </c>
+      <c r="N49" s="4" t="inlineStr">
+        <is>
+          <t>7.87</t>
+        </is>
+      </c>
+      <c r="O49" s="4" t="inlineStr">
+        <is>
+          <t>6.11</t>
+        </is>
+      </c>
+      <c r="P49" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁公开页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="D50" s="4" t="inlineStr"/>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>1.7137</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>2.5263</v>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K50" s="7" t="inlineStr">
+        <is>
+          <t>未进入加大买入区间</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="M50" s="4" t="inlineStr">
+        <is>
+          <t>4.34</t>
+        </is>
+      </c>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>10.34</t>
+        </is>
+      </c>
+      <c r="O50" s="4" t="inlineStr">
+        <is>
+          <t>6.11</t>
+        </is>
+      </c>
+      <c r="P50" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁公开页面</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P48"/>
+  <autoFilter ref="A1:P50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P50"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3414,7 +3414,7 @@
       <c r="C50" s="4" t="n">
         <v>4.24</v>
       </c>
-      <c r="D50" s="4" t="inlineStr"/>
+      <c r="D50" s="4" t="n"/>
       <c r="E50" s="3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
@@ -3472,8 +3472,60 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="D51" s="4" t="inlineStr"/>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>1.7143</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>2.475700000000001</v>
+      </c>
+      <c r="H51" s="6" t="inlineStr"/>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr"/>
+      <c r="M51" s="4" t="inlineStr"/>
+      <c r="N51" s="4" t="inlineStr"/>
+      <c r="O51" s="4" t="inlineStr"/>
+      <c r="P51" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P50"/>
+  <autoFilter ref="A1:P51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P51"/>
+  <dimension ref="A1:P54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3486,7 +3486,7 @@
       <c r="C51" s="4" t="n">
         <v>4.19</v>
       </c>
-      <c r="D51" s="4" t="inlineStr"/>
+      <c r="D51" s="4" t="n"/>
       <c r="E51" s="3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
@@ -3514,18 +3514,194 @@
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L51" s="3" t="inlineStr"/>
-      <c r="M51" s="4" t="inlineStr"/>
-      <c r="N51" s="4" t="inlineStr"/>
-      <c r="O51" s="4" t="inlineStr"/>
+      <c r="L51" s="3" t="n"/>
+      <c r="M51" s="4" t="n"/>
+      <c r="N51" s="4" t="n"/>
+      <c r="O51" s="4" t="n"/>
       <c r="P51" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>1.7114</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>2.4886</v>
+      </c>
+      <c r="H52" s="6" t="inlineStr"/>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K52" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="n"/>
+      <c r="M52" s="4" t="n"/>
+      <c r="N52" s="4" t="n"/>
+      <c r="O52" s="4" t="n"/>
+      <c r="P52" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>1.7074</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>2.4526</v>
+      </c>
+      <c r="H53" s="6" t="inlineStr"/>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="n"/>
+      <c r="M53" s="4" t="n"/>
+      <c r="N53" s="4" t="n"/>
+      <c r="O53" s="4" t="n"/>
+      <c r="P53" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="D54" s="4" t="inlineStr"/>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>1.7161</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>2.4639</v>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K54" s="7" t="inlineStr">
+        <is>
+          <t>未进入加大买入区间</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="M54" s="4" t="inlineStr">
+        <is>
+          <t>4.26</t>
+        </is>
+      </c>
+      <c r="N54" s="4" t="inlineStr">
+        <is>
+          <t>7.04</t>
+        </is>
+      </c>
+      <c r="O54" s="4" t="inlineStr">
+        <is>
+          <t>6.11</t>
+        </is>
+      </c>
+      <c r="P54" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁公开页面</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P51"/>
+  <autoFilter ref="A1:P54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P54"/>
+  <dimension ref="A1:P55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3642,7 +3642,7 @@
       <c r="C54" s="4" t="n">
         <v>4.18</v>
       </c>
-      <c r="D54" s="4" t="inlineStr"/>
+      <c r="D54" s="4" t="n"/>
       <c r="E54" s="3" t="inlineStr">
         <is>
           <t>2026-08-11</t>
@@ -3700,8 +3700,60 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="D55" s="4" t="inlineStr"/>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>1.7141</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>2.4759</v>
+      </c>
+      <c r="H55" s="6" t="inlineStr"/>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr"/>
+      <c r="M55" s="4" t="inlineStr"/>
+      <c r="N55" s="4" t="inlineStr"/>
+      <c r="O55" s="4" t="inlineStr"/>
+      <c r="P55" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P54"/>
+  <autoFilter ref="A1:P55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P55"/>
+  <dimension ref="A1:P57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3714,7 +3714,7 @@
       <c r="C55" s="4" t="n">
         <v>4.19</v>
       </c>
-      <c r="D55" s="4" t="inlineStr"/>
+      <c r="D55" s="4" t="n"/>
       <c r="E55" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
@@ -3742,18 +3742,142 @@
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L55" s="3" t="inlineStr"/>
-      <c r="M55" s="4" t="inlineStr"/>
-      <c r="N55" s="4" t="inlineStr"/>
-      <c r="O55" s="4" t="inlineStr"/>
+      <c r="L55" s="3" t="n"/>
+      <c r="M55" s="4" t="n"/>
+      <c r="N55" s="4" t="n"/>
+      <c r="O55" s="4" t="n"/>
       <c r="P55" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="D56" s="4" t="n"/>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>1.7032</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>2.526800000000001</v>
+      </c>
+      <c r="H56" s="6" t="inlineStr"/>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K56" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="n"/>
+      <c r="M56" s="4" t="n"/>
+      <c r="N56" s="4" t="n"/>
+      <c r="O56" s="4" t="n"/>
+      <c r="P56" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="D57" s="4" t="inlineStr"/>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>1.6964</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>2.5236</v>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>未进入加大买入区间</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="M57" s="4" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="N57" s="4" t="inlineStr">
+        <is>
+          <t>8.95</t>
+        </is>
+      </c>
+      <c r="O57" s="4" t="inlineStr">
+        <is>
+          <t>6.11</t>
+        </is>
+      </c>
+      <c r="P57" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁公开页面</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P55"/>
+  <autoFilter ref="A1:P57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P57"/>
+  <dimension ref="A1:P59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3818,7 +3818,7 @@
       <c r="C57" s="4" t="n">
         <v>4.22</v>
       </c>
-      <c r="D57" s="4" t="inlineStr"/>
+      <c r="D57" s="4" t="n"/>
       <c r="E57" s="3" t="inlineStr">
         <is>
           <t>2026-08-14</t>
@@ -3876,8 +3876,112 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>1.6924</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>2.5076</v>
+      </c>
+      <c r="H58" s="6" t="inlineStr"/>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K58" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="n"/>
+      <c r="M58" s="4" t="n"/>
+      <c r="N58" s="4" t="n"/>
+      <c r="O58" s="4" t="n"/>
+      <c r="P58" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="D59" s="4" t="inlineStr"/>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>1.6864</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>2.4836</v>
+      </c>
+      <c r="H59" s="6" t="inlineStr"/>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr"/>
+      <c r="M59" s="4" t="inlineStr"/>
+      <c r="N59" s="4" t="inlineStr"/>
+      <c r="O59" s="4" t="inlineStr"/>
+      <c r="P59" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P57"/>
+  <autoFilter ref="A1:P59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sources/automations/中证红利信号/中证红利每日信号.xlsx
+++ b/sources/automations/中证红利信号/中证红利每日信号.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证红利每日信号" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$P$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中证红利每日信号'!$A$1:$R$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,25 +493,27 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P59"/>
+  <dimension ref="A1:R61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="25" customWidth="1" min="13" max="13"/>
-    <col width="25" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="15" max="15"/>
+    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -532,65 +534,75 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>ytd_return</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ytd_max_drawdown</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>xueqiu_change_percent</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>bond_date__china_10y_yield_date</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>bond_10y_yield</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>spread</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>percentile_signal</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>absolute_signal</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>spread_signal</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>headline_signal</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>lixinger_date__percentile_source_date</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>lixinger_dividend_yield</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>lixinger_percentile_10y</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>lixinger_percentile_80_value</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>lixinger_source</t>
         </is>
@@ -614,65 +626,75 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>全年收益率(%)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>年内最大回撤(%)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>雪球当天涨跌幅(%)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>中国10年国债收益率日期</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>中国10年国债收益率(%)</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>股债利差:股息率2-10年国债收益率(百分点)</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>历史分位点触发</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>绝对股息率触发</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>股债利差触发</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>综合结论</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>理杏仁估值日期</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>理杏仁市值加权股息率(%)</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>理杏仁近10年股息率分位(%)</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>理杏仁近10年80%分位点(%)</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>理杏仁数据源状态</t>
         </is>
@@ -695,42 +717,44 @@
         </is>
       </c>
       <c r="D3" s="4" t="n"/>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>2026/6/2</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>1.7036</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>3.1264</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr"/>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr"/>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K3" s="7" t="inlineStr">
+      <c r="M3" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L3" s="3" t="n"/>
-      <c r="M3" s="4" t="n"/>
-      <c r="N3" s="4" t="n"/>
+      <c r="N3" s="3" t="n"/>
       <c r="O3" s="4" t="n"/>
-      <c r="P3" s="7" t="inlineStr">
+      <c r="P3" s="4" t="n"/>
+      <c r="Q3" s="4" t="n"/>
+      <c r="R3" s="7" t="inlineStr">
         <is>
           <t>理杏仁限流</t>
         </is>
@@ -753,42 +777,44 @@
         </is>
       </c>
       <c r="D4" s="4" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>2026/6/3</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>1.7128</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>3.1172</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr"/>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr"/>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L4" s="3" t="n"/>
-      <c r="M4" s="4" t="n"/>
-      <c r="N4" s="4" t="n"/>
+      <c r="N4" s="3" t="n"/>
       <c r="O4" s="4" t="n"/>
-      <c r="P4" s="7" t="inlineStr">
+      <c r="P4" s="4" t="n"/>
+      <c r="Q4" s="4" t="n"/>
+      <c r="R4" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -811,42 +837,44 @@
         </is>
       </c>
       <c r="D5" s="4" t="n"/>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>2026/6/4</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>1.7081</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>3.1419</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr"/>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr"/>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L5" s="3" t="n"/>
-      <c r="M5" s="4" t="n"/>
-      <c r="N5" s="4" t="n"/>
+      <c r="N5" s="3" t="n"/>
       <c r="O5" s="4" t="n"/>
-      <c r="P5" s="7" t="inlineStr">
+      <c r="P5" s="4" t="n"/>
+      <c r="Q5" s="4" t="n"/>
+      <c r="R5" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -867,38 +895,40 @@
         <v>4.9</v>
       </c>
       <c r="D6" s="4" t="n"/>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="H6" s="5" t="n">
         <v>1.7275</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="I6" s="5" t="n">
         <v>3.1725</v>
       </c>
-      <c r="H6" s="6" t="inlineStr"/>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr"/>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K6" s="7" t="inlineStr">
+      <c r="M6" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L6" s="3" t="n"/>
-      <c r="M6" s="4" t="n"/>
-      <c r="N6" s="4" t="n"/>
+      <c r="N6" s="3" t="n"/>
       <c r="O6" s="4" t="n"/>
-      <c r="P6" s="7" t="inlineStr">
+      <c r="P6" s="4" t="n"/>
+      <c r="Q6" s="4" t="n"/>
+      <c r="R6" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -919,38 +949,40 @@
         <v>4.9</v>
       </c>
       <c r="D7" s="4" t="n"/>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="H7" s="5" t="n">
         <v>1.7376</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="I7" s="5" t="n">
         <v>3.1624</v>
       </c>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr"/>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L7" s="3" t="n"/>
-      <c r="M7" s="4" t="n"/>
-      <c r="N7" s="4" t="n"/>
+      <c r="N7" s="3" t="n"/>
       <c r="O7" s="4" t="n"/>
-      <c r="P7" s="7" t="inlineStr">
+      <c r="P7" s="4" t="n"/>
+      <c r="Q7" s="4" t="n"/>
+      <c r="R7" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -971,38 +1003,40 @@
         <v>4.93</v>
       </c>
       <c r="D8" s="4" t="n"/>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="H8" s="5" t="n">
         <v>1.7476</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="I8" s="5" t="n">
         <v>3.182399999999999</v>
       </c>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr"/>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K8" s="7" t="inlineStr">
+      <c r="M8" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L8" s="3" t="n"/>
-      <c r="M8" s="4" t="n"/>
-      <c r="N8" s="4" t="n"/>
+      <c r="N8" s="3" t="n"/>
       <c r="O8" s="4" t="n"/>
-      <c r="P8" s="7" t="inlineStr">
+      <c r="P8" s="4" t="n"/>
+      <c r="Q8" s="4" t="n"/>
+      <c r="R8" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -1023,38 +1057,40 @@
         <v>4.95</v>
       </c>
       <c r="D9" s="4" t="n"/>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="H9" s="5" t="n">
         <v>1.7475</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="I9" s="5" t="n">
         <v>3.2025</v>
       </c>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr"/>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K9" s="7" t="inlineStr">
+      <c r="M9" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L9" s="3" t="n"/>
-      <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="n"/>
+      <c r="N9" s="3" t="n"/>
       <c r="O9" s="4" t="n"/>
-      <c r="P9" s="7" t="inlineStr">
+      <c r="P9" s="4" t="n"/>
+      <c r="Q9" s="4" t="n"/>
+      <c r="R9" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -1075,38 +1111,40 @@
         <v>4.88</v>
       </c>
       <c r="D10" s="4" t="n"/>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="H10" s="5" t="n">
         <v>1.7427</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="I10" s="5" t="n">
         <v>3.1373</v>
       </c>
-      <c r="H10" s="6" t="inlineStr"/>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
+      <c r="J10" s="6" t="inlineStr"/>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K10" s="7" t="inlineStr">
+      <c r="M10" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L10" s="3" t="n"/>
-      <c r="M10" s="4" t="n"/>
-      <c r="N10" s="4" t="n"/>
+      <c r="N10" s="3" t="n"/>
       <c r="O10" s="4" t="n"/>
-      <c r="P10" s="7" t="inlineStr">
+      <c r="P10" s="4" t="n"/>
+      <c r="Q10" s="4" t="n"/>
+      <c r="R10" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -1127,38 +1165,40 @@
         <v>5.03</v>
       </c>
       <c r="D11" s="9" t="n"/>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="H11" s="10" t="n">
         <v>1.7324</v>
       </c>
-      <c r="G11" s="10" t="n">
+      <c r="I11" s="10" t="n">
         <v>3.2976</v>
       </c>
-      <c r="H11" s="11" t="inlineStr"/>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr"/>
+      <c r="K11" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="L11" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K11" s="12" t="inlineStr">
+      <c r="M11" s="12" t="inlineStr">
         <is>
           <t>加大买入区间</t>
         </is>
       </c>
-      <c r="L11" s="8" t="n"/>
-      <c r="M11" s="9" t="n"/>
-      <c r="N11" s="9" t="n"/>
+      <c r="N11" s="8" t="n"/>
       <c r="O11" s="9" t="n"/>
-      <c r="P11" s="12" t="inlineStr">
+      <c r="P11" s="9" t="n"/>
+      <c r="Q11" s="9" t="n"/>
+      <c r="R11" s="12" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -1179,38 +1219,40 @@
         <v>5.08</v>
       </c>
       <c r="D12" s="9" t="n"/>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="9" t="n"/>
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="H12" s="10" t="n">
         <v>1.727</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="I12" s="10" t="n">
         <v>3.353</v>
       </c>
-      <c r="H12" s="11" t="inlineStr"/>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr"/>
+      <c r="K12" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="L12" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K12" s="12" t="inlineStr">
+      <c r="M12" s="12" t="inlineStr">
         <is>
           <t>加大买入区间</t>
         </is>
       </c>
-      <c r="L12" s="8" t="n"/>
-      <c r="M12" s="9" t="n"/>
-      <c r="N12" s="9" t="n"/>
+      <c r="N12" s="8" t="n"/>
       <c r="O12" s="9" t="n"/>
-      <c r="P12" s="12" t="inlineStr">
+      <c r="P12" s="9" t="n"/>
+      <c r="Q12" s="9" t="n"/>
+      <c r="R12" s="12" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -1231,38 +1273,40 @@
         <v>5.19</v>
       </c>
       <c r="D13" s="9" t="n"/>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="H13" s="10" t="n">
         <v>1.7299</v>
       </c>
-      <c r="G13" s="10" t="n">
+      <c r="I13" s="10" t="n">
         <v>3.460100000000001</v>
       </c>
-      <c r="H13" s="11" t="inlineStr"/>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr"/>
+      <c r="K13" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="L13" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K13" s="12" t="inlineStr">
+      <c r="M13" s="12" t="inlineStr">
         <is>
           <t>加大买入区间</t>
         </is>
       </c>
-      <c r="L13" s="8" t="n"/>
-      <c r="M13" s="9" t="n"/>
-      <c r="N13" s="9" t="n"/>
+      <c r="N13" s="8" t="n"/>
       <c r="O13" s="9" t="n"/>
-      <c r="P13" s="12" t="inlineStr">
+      <c r="P13" s="9" t="n"/>
+      <c r="Q13" s="9" t="n"/>
+      <c r="R13" s="12" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -1283,38 +1327,40 @@
         <v>5.14</v>
       </c>
       <c r="D14" s="9" t="n"/>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n">
+      <c r="H14" s="10" t="n">
         <v>1.7375</v>
       </c>
-      <c r="G14" s="10" t="n">
+      <c r="I14" s="10" t="n">
         <v>3.4025</v>
       </c>
-      <c r="H14" s="11" t="inlineStr"/>
-      <c r="I14" s="11" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr"/>
+      <c r="K14" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="L14" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K14" s="12" t="inlineStr">
+      <c r="M14" s="12" t="inlineStr">
         <is>
           <t>加大买入区间</t>
         </is>
       </c>
-      <c r="L14" s="8" t="n"/>
-      <c r="M14" s="9" t="n"/>
-      <c r="N14" s="9" t="n"/>
+      <c r="N14" s="8" t="n"/>
       <c r="O14" s="9" t="n"/>
-      <c r="P14" s="12" t="inlineStr">
+      <c r="P14" s="9" t="n"/>
+      <c r="Q14" s="9" t="n"/>
+      <c r="R14" s="12" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -1335,38 +1381,40 @@
         <v>5.17</v>
       </c>
       <c r="D15" s="9" t="n"/>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="F15" s="10" t="n">
+      <c r="H15" s="10" t="n">
         <v>1.7437</v>
       </c>
-      <c r="G15" s="10" t="n">
+      <c r="I15" s="10" t="n">
         <v>3.4263</v>
       </c>
-      <c r="H15" s="11" t="inlineStr"/>
-      <c r="I15" s="11" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr"/>
+      <c r="K15" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr">
+      <c r="L15" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K15" s="12" t="inlineStr">
+      <c r="M15" s="12" t="inlineStr">
         <is>
           <t>加大买入区间</t>
         </is>
       </c>
-      <c r="L15" s="8" t="n"/>
-      <c r="M15" s="9" t="n"/>
-      <c r="N15" s="9" t="n"/>
+      <c r="N15" s="8" t="n"/>
       <c r="O15" s="9" t="n"/>
-      <c r="P15" s="12" t="inlineStr">
+      <c r="P15" s="9" t="n"/>
+      <c r="Q15" s="9" t="n"/>
+      <c r="R15" s="12" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -1387,38 +1435,40 @@
         <v>5.25</v>
       </c>
       <c r="D16" s="9" t="n"/>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n">
+      <c r="H16" s="10" t="n">
         <v>1.7454</v>
       </c>
-      <c r="G16" s="10" t="n">
+      <c r="I16" s="10" t="n">
         <v>3.5046</v>
       </c>
-      <c r="H16" s="11" t="inlineStr"/>
-      <c r="I16" s="11" t="inlineStr">
+      <c r="J16" s="11" t="inlineStr"/>
+      <c r="K16" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="L16" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K16" s="12" t="inlineStr">
+      <c r="M16" s="12" t="inlineStr">
         <is>
           <t>加大买入区间</t>
         </is>
       </c>
-      <c r="L16" s="8" t="n"/>
-      <c r="M16" s="9" t="n"/>
-      <c r="N16" s="9" t="n"/>
+      <c r="N16" s="8" t="n"/>
       <c r="O16" s="9" t="n"/>
-      <c r="P16" s="12" t="inlineStr">
+      <c r="P16" s="9" t="n"/>
+      <c r="Q16" s="9" t="n"/>
+      <c r="R16" s="12" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -1439,38 +1489,40 @@
         <v>5.31</v>
       </c>
       <c r="D17" s="9" t="n"/>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="H17" s="10" t="n">
         <v>1.7351</v>
       </c>
-      <c r="G17" s="10" t="n">
+      <c r="I17" s="10" t="n">
         <v>3.5749</v>
       </c>
-      <c r="H17" s="11" t="inlineStr"/>
-      <c r="I17" s="11" t="inlineStr">
+      <c r="J17" s="11" t="inlineStr"/>
+      <c r="K17" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="L17" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K17" s="12" t="inlineStr">
+      <c r="M17" s="12" t="inlineStr">
         <is>
           <t>加大买入区间</t>
         </is>
       </c>
-      <c r="L17" s="8" t="n"/>
-      <c r="M17" s="9" t="n"/>
-      <c r="N17" s="9" t="n"/>
+      <c r="N17" s="8" t="n"/>
       <c r="O17" s="9" t="n"/>
-      <c r="P17" s="12" t="inlineStr">
+      <c r="P17" s="9" t="n"/>
+      <c r="Q17" s="9" t="n"/>
+      <c r="R17" s="12" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -1491,38 +1543,40 @@
         <v>5.43</v>
       </c>
       <c r="D18" s="9" t="n"/>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="F18" s="10" t="n">
+      <c r="H18" s="10" t="n">
         <v>1.7314</v>
       </c>
-      <c r="G18" s="10" t="n">
+      <c r="I18" s="10" t="n">
         <v>3.6986</v>
       </c>
-      <c r="H18" s="11" t="inlineStr"/>
-      <c r="I18" s="11" t="inlineStr">
+      <c r="J18" s="11" t="inlineStr"/>
+      <c r="K18" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="L18" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K18" s="12" t="inlineStr">
+      <c r="M18" s="12" t="inlineStr">
         <is>
           <t>加大买入区间</t>
         </is>
       </c>
-      <c r="L18" s="8" t="n"/>
-      <c r="M18" s="9" t="n"/>
-      <c r="N18" s="9" t="n"/>
+      <c r="N18" s="8" t="n"/>
       <c r="O18" s="9" t="n"/>
-      <c r="P18" s="12" t="inlineStr">
+      <c r="P18" s="9" t="n"/>
+      <c r="Q18" s="9" t="n"/>
+      <c r="R18" s="12" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -1543,38 +1597,40 @@
         <v>5.43</v>
       </c>
       <c r="D19" s="9" t="n"/>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="F19" s="10" t="n">
+      <c r="H19" s="10" t="n">
         <v>1.7314</v>
       </c>
-      <c r="G19" s="10" t="n">
+      <c r="I19" s="10" t="n">
         <v>3.6986</v>
       </c>
-      <c r="H19" s="11" t="inlineStr"/>
-      <c r="I19" s="11" t="inlineStr">
+      <c r="J19" s="11" t="inlineStr"/>
+      <c r="K19" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr">
+      <c r="L19" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K19" s="12" t="inlineStr">
+      <c r="M19" s="12" t="inlineStr">
         <is>
           <t>加大买入区间</t>
         </is>
       </c>
-      <c r="L19" s="8" t="n"/>
-      <c r="M19" s="9" t="n"/>
-      <c r="N19" s="9" t="n"/>
+      <c r="N19" s="8" t="n"/>
       <c r="O19" s="9" t="n"/>
-      <c r="P19" s="12" t="inlineStr">
+      <c r="P19" s="9" t="n"/>
+      <c r="Q19" s="9" t="n"/>
+      <c r="R19" s="12" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -1595,38 +1651,40 @@
         <v>5.43</v>
       </c>
       <c r="D20" s="9" t="n"/>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="F20" s="10" t="n">
+      <c r="H20" s="10" t="n">
         <v>1.7314</v>
       </c>
-      <c r="G20" s="10" t="n">
+      <c r="I20" s="10" t="n">
         <v>3.6986</v>
       </c>
-      <c r="H20" s="11" t="inlineStr"/>
-      <c r="I20" s="11" t="inlineStr">
+      <c r="J20" s="11" t="inlineStr"/>
+      <c r="K20" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="L20" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K20" s="12" t="inlineStr">
+      <c r="M20" s="12" t="inlineStr">
         <is>
           <t>加大买入区间</t>
         </is>
       </c>
-      <c r="L20" s="8" t="n"/>
-      <c r="M20" s="9" t="n"/>
-      <c r="N20" s="9" t="n"/>
+      <c r="N20" s="8" t="n"/>
       <c r="O20" s="9" t="n"/>
-      <c r="P20" s="12" t="inlineStr">
+      <c r="P20" s="9" t="n"/>
+      <c r="Q20" s="9" t="n"/>
+      <c r="R20" s="12" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -1647,38 +1705,40 @@
         <v>5.39</v>
       </c>
       <c r="D21" s="9" t="n"/>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="F21" s="10" t="n">
+      <c r="H21" s="10" t="n">
         <v>1.717</v>
       </c>
-      <c r="G21" s="10" t="n">
+      <c r="I21" s="10" t="n">
         <v>3.673</v>
       </c>
-      <c r="H21" s="11" t="inlineStr"/>
-      <c r="I21" s="11" t="inlineStr">
+      <c r="J21" s="11" t="inlineStr"/>
+      <c r="K21" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr">
+      <c r="L21" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K21" s="12" t="inlineStr">
+      <c r="M21" s="12" t="inlineStr">
         <is>
           <t>加大买入区间</t>
         </is>
       </c>
-      <c r="L21" s="8" t="n"/>
-      <c r="M21" s="9" t="n"/>
-      <c r="N21" s="9" t="n"/>
+      <c r="N21" s="8" t="n"/>
       <c r="O21" s="9" t="n"/>
-      <c r="P21" s="12" t="inlineStr">
+      <c r="P21" s="9" t="n"/>
+      <c r="Q21" s="9" t="n"/>
+      <c r="R21" s="12" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -1699,38 +1759,40 @@
         <v>4.84</v>
       </c>
       <c r="D22" s="4" t="n"/>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="H22" s="5" t="n">
         <v>1.733</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="I22" s="5" t="n">
         <v>3.107</v>
       </c>
-      <c r="H22" s="6" t="inlineStr"/>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
+      <c r="J22" s="6" t="inlineStr"/>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K22" s="7" t="inlineStr">
+      <c r="M22" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L22" s="3" t="n"/>
-      <c r="M22" s="4" t="n"/>
-      <c r="N22" s="4" t="n"/>
+      <c r="N22" s="3" t="n"/>
       <c r="O22" s="4" t="n"/>
-      <c r="P22" s="7" t="inlineStr">
+      <c r="P22" s="4" t="n"/>
+      <c r="Q22" s="4" t="n"/>
+      <c r="R22" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -1751,38 +1813,40 @@
         <v>4.76</v>
       </c>
       <c r="D23" s="4" t="n"/>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="H23" s="5" t="n">
         <v>1.7448</v>
       </c>
-      <c r="G23" s="5" t="n">
+      <c r="I23" s="5" t="n">
         <v>3.0152</v>
       </c>
-      <c r="H23" s="6" t="inlineStr"/>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
+      <c r="J23" s="6" t="inlineStr"/>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K23" s="7" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L23" s="3" t="n"/>
-      <c r="M23" s="4" t="n"/>
-      <c r="N23" s="4" t="n"/>
+      <c r="N23" s="3" t="n"/>
       <c r="O23" s="4" t="n"/>
-      <c r="P23" s="7" t="inlineStr">
+      <c r="P23" s="4" t="n"/>
+      <c r="Q23" s="4" t="n"/>
+      <c r="R23" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -1803,38 +1867,40 @@
         <v>4.72</v>
       </c>
       <c r="D24" s="4" t="n"/>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="H24" s="5" t="n">
         <v>1.741</v>
       </c>
-      <c r="G24" s="5" t="n">
+      <c r="I24" s="5" t="n">
         <v>2.979</v>
       </c>
-      <c r="H24" s="6" t="inlineStr"/>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J24" s="6" t="inlineStr">
+      <c r="J24" s="6" t="inlineStr"/>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K24" s="7" t="inlineStr">
+      <c r="M24" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L24" s="3" t="n"/>
-      <c r="M24" s="4" t="n"/>
-      <c r="N24" s="4" t="n"/>
+      <c r="N24" s="3" t="n"/>
       <c r="O24" s="4" t="n"/>
-      <c r="P24" s="7" t="inlineStr">
+      <c r="P24" s="4" t="n"/>
+      <c r="Q24" s="4" t="n"/>
+      <c r="R24" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -1855,38 +1921,40 @@
         <v>4.67</v>
       </c>
       <c r="D25" s="4" t="n"/>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="F25" s="5" t="n">
+      <c r="H25" s="5" t="n">
         <v>1.7463</v>
       </c>
-      <c r="G25" s="5" t="n">
+      <c r="I25" s="5" t="n">
         <v>2.9237</v>
       </c>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J25" s="6" t="inlineStr">
+      <c r="J25" s="6" t="inlineStr"/>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K25" s="7" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L25" s="3" t="n"/>
-      <c r="M25" s="4" t="n"/>
-      <c r="N25" s="4" t="n"/>
+      <c r="N25" s="3" t="n"/>
       <c r="O25" s="4" t="n"/>
-      <c r="P25" s="7" t="inlineStr">
+      <c r="P25" s="4" t="n"/>
+      <c r="Q25" s="4" t="n"/>
+      <c r="R25" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -1907,38 +1975,40 @@
         <v>4.67</v>
       </c>
       <c r="D26" s="4" t="n"/>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="F26" s="5" t="n">
+      <c r="H26" s="5" t="n">
         <v>1.7463</v>
       </c>
-      <c r="G26" s="5" t="n">
+      <c r="I26" s="5" t="n">
         <v>2.9237</v>
       </c>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J26" s="6" t="inlineStr">
+      <c r="J26" s="6" t="inlineStr"/>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L26" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K26" s="7" t="inlineStr">
+      <c r="M26" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L26" s="3" t="n"/>
-      <c r="M26" s="4" t="n"/>
-      <c r="N26" s="4" t="n"/>
+      <c r="N26" s="3" t="n"/>
       <c r="O26" s="4" t="n"/>
-      <c r="P26" s="7" t="inlineStr">
+      <c r="P26" s="4" t="n"/>
+      <c r="Q26" s="4" t="n"/>
+      <c r="R26" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -1959,38 +2029,40 @@
         <v>4.67</v>
       </c>
       <c r="D27" s="4" t="n"/>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="H27" s="5" t="n">
         <v>1.7463</v>
       </c>
-      <c r="G27" s="5" t="n">
+      <c r="I27" s="5" t="n">
         <v>2.9237</v>
       </c>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
+      <c r="J27" s="6" t="inlineStr"/>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L27" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K27" s="7" t="inlineStr">
+      <c r="M27" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L27" s="3" t="n"/>
-      <c r="M27" s="4" t="n"/>
-      <c r="N27" s="4" t="n"/>
+      <c r="N27" s="3" t="n"/>
       <c r="O27" s="4" t="n"/>
-      <c r="P27" s="7" t="inlineStr">
+      <c r="P27" s="4" t="n"/>
+      <c r="Q27" s="4" t="n"/>
+      <c r="R27" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -2011,58 +2083,60 @@
         <v>4.67</v>
       </c>
       <c r="D28" s="4" t="n"/>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="F28" s="5" t="n">
+      <c r="H28" s="5" t="n">
         <v>1.7463</v>
       </c>
-      <c r="G28" s="5" t="n">
+      <c r="I28" s="5" t="n">
         <v>2.9237</v>
       </c>
-      <c r="H28" s="6" t="inlineStr">
+      <c r="J28" s="6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J28" s="6" t="inlineStr">
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L28" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K28" s="7" t="inlineStr">
+      <c r="M28" s="7" t="inlineStr">
         <is>
           <t>未进入加大买入区间</t>
         </is>
       </c>
-      <c r="L28" s="3" t="inlineStr">
+      <c r="N28" s="3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="M28" s="4" t="inlineStr">
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <t>4.58</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="P28" s="4" t="inlineStr">
         <is>
           <t>27.21</t>
         </is>
       </c>
-      <c r="O28" s="4" t="inlineStr">
+      <c r="Q28" s="4" t="inlineStr">
         <is>
           <t>6.12</t>
         </is>
       </c>
-      <c r="P28" s="7" t="inlineStr">
+      <c r="R28" s="7" t="inlineStr">
         <is>
           <t>理杏仁公开页面</t>
         </is>
@@ -2083,38 +2157,40 @@
         <v>4.57</v>
       </c>
       <c r="D29" s="4" t="n"/>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="H29" s="5" t="n">
         <v>1.7379</v>
       </c>
-      <c r="G29" s="5" t="n">
+      <c r="I29" s="5" t="n">
         <v>2.832100000000001</v>
       </c>
-      <c r="H29" s="6" t="inlineStr"/>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J29" s="6" t="inlineStr">
+      <c r="J29" s="6" t="inlineStr"/>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K29" s="7" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L29" s="3" t="n"/>
-      <c r="M29" s="4" t="n"/>
-      <c r="N29" s="4" t="n"/>
+      <c r="N29" s="3" t="n"/>
       <c r="O29" s="4" t="n"/>
-      <c r="P29" s="7" t="inlineStr">
+      <c r="P29" s="4" t="n"/>
+      <c r="Q29" s="4" t="n"/>
+      <c r="R29" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -2135,38 +2211,40 @@
         <v>4.64</v>
       </c>
       <c r="D30" s="4" t="n"/>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="F30" s="5" t="n">
+      <c r="H30" s="5" t="n">
         <v>1.7406</v>
       </c>
-      <c r="G30" s="5" t="n">
+      <c r="I30" s="5" t="n">
         <v>2.8994</v>
       </c>
-      <c r="H30" s="6" t="inlineStr"/>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J30" s="6" t="inlineStr">
+      <c r="J30" s="6" t="inlineStr"/>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L30" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K30" s="7" t="inlineStr">
+      <c r="M30" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L30" s="3" t="n"/>
-      <c r="M30" s="4" t="n"/>
-      <c r="N30" s="4" t="n"/>
+      <c r="N30" s="3" t="n"/>
       <c r="O30" s="4" t="n"/>
-      <c r="P30" s="7" t="inlineStr">
+      <c r="P30" s="4" t="n"/>
+      <c r="Q30" s="4" t="n"/>
+      <c r="R30" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -2187,58 +2265,60 @@
         <v>4.62</v>
       </c>
       <c r="D31" s="4" t="n"/>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="F31" s="5" t="n">
+      <c r="H31" s="5" t="n">
         <v>1.7385</v>
       </c>
-      <c r="G31" s="5" t="n">
+      <c r="I31" s="5" t="n">
         <v>2.8815</v>
       </c>
-      <c r="H31" s="6" t="inlineStr">
+      <c r="J31" s="6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J31" s="6" t="inlineStr">
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L31" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K31" s="7" t="inlineStr">
+      <c r="M31" s="7" t="inlineStr">
         <is>
           <t>未进入加大买入区间</t>
         </is>
       </c>
-      <c r="L31" s="3" t="inlineStr">
+      <c r="N31" s="3" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="M31" s="4" t="inlineStr">
+      <c r="O31" s="4" t="inlineStr">
         <is>
           <t>4.49</t>
         </is>
       </c>
-      <c r="N31" s="4" t="inlineStr">
+      <c r="P31" s="4" t="inlineStr">
         <is>
           <t>23.03</t>
         </is>
       </c>
-      <c r="O31" s="4" t="inlineStr">
+      <c r="Q31" s="4" t="inlineStr">
         <is>
           <t>6.12</t>
         </is>
       </c>
-      <c r="P31" s="7" t="inlineStr">
+      <c r="R31" s="7" t="inlineStr">
         <is>
           <t>理杏仁公开页面</t>
         </is>
@@ -2259,58 +2339,60 @@
         <v>4.67</v>
       </c>
       <c r="D32" s="4" t="n"/>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="F32" s="5" t="n">
+      <c r="H32" s="5" t="n">
         <v>1.7376</v>
       </c>
-      <c r="G32" s="5" t="n">
+      <c r="I32" s="5" t="n">
         <v>2.9324</v>
       </c>
-      <c r="H32" s="6" t="inlineStr">
+      <c r="J32" s="6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J32" s="6" t="inlineStr">
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L32" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K32" s="7" t="inlineStr">
+      <c r="M32" s="7" t="inlineStr">
         <is>
           <t>未进入加大买入区间</t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
+      <c r="N32" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="M32" s="4" t="inlineStr">
+      <c r="O32" s="4" t="inlineStr">
         <is>
           <t>4.54</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="P32" s="4" t="inlineStr">
         <is>
           <t>26.17</t>
         </is>
       </c>
-      <c r="O32" s="4" t="inlineStr">
+      <c r="Q32" s="4" t="inlineStr">
         <is>
           <t>6.12</t>
         </is>
       </c>
-      <c r="P32" s="7" t="inlineStr">
+      <c r="R32" s="7" t="inlineStr">
         <is>
           <t>理杏仁公开页面</t>
         </is>
@@ -2331,58 +2413,60 @@
         <v>4.69</v>
       </c>
       <c r="D33" s="4" t="n"/>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="F33" s="5" t="n">
+      <c r="H33" s="5" t="n">
         <v>1.7398</v>
       </c>
-      <c r="G33" s="5" t="n">
+      <c r="I33" s="5" t="n">
         <v>2.950200000000001</v>
       </c>
-      <c r="H33" s="6" t="inlineStr">
+      <c r="J33" s="6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J33" s="6" t="inlineStr">
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L33" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K33" s="7" t="inlineStr">
+      <c r="M33" s="7" t="inlineStr">
         <is>
           <t>未进入加大买入区间</t>
         </is>
       </c>
-      <c r="L33" s="3" t="inlineStr">
+      <c r="N33" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="M33" s="4" t="inlineStr">
+      <c r="O33" s="4" t="inlineStr">
         <is>
           <t>4.53</t>
         </is>
       </c>
-      <c r="N33" s="4" t="inlineStr">
+      <c r="P33" s="4" t="inlineStr">
         <is>
           <t>25.76</t>
         </is>
       </c>
-      <c r="O33" s="4" t="inlineStr">
+      <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>6.12</t>
         </is>
       </c>
-      <c r="P33" s="7" t="inlineStr">
+      <c r="R33" s="7" t="inlineStr">
         <is>
           <t>理杏仁公开页面</t>
         </is>
@@ -2403,58 +2487,60 @@
         <v>4.68</v>
       </c>
       <c r="D34" s="4" t="n"/>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="F34" s="5" t="n">
+      <c r="H34" s="5" t="n">
         <v>1.7442</v>
       </c>
-      <c r="G34" s="5" t="n">
+      <c r="I34" s="5" t="n">
         <v>2.9358</v>
       </c>
-      <c r="H34" s="6" t="inlineStr">
+      <c r="J34" s="6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J34" s="6" t="inlineStr">
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L34" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K34" s="7" t="inlineStr">
+      <c r="M34" s="7" t="inlineStr">
         <is>
           <t>未进入加大买入区间</t>
         </is>
       </c>
-      <c r="L34" s="3" t="inlineStr">
+      <c r="N34" s="3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="M34" s="4" t="inlineStr">
+      <c r="O34" s="4" t="inlineStr">
         <is>
           <t>4.45</t>
         </is>
       </c>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="P34" s="4" t="inlineStr">
         <is>
           <t>18.78</t>
         </is>
       </c>
-      <c r="O34" s="4" t="inlineStr">
+      <c r="Q34" s="4" t="inlineStr">
         <is>
           <t>6.12</t>
         </is>
       </c>
-      <c r="P34" s="7" t="inlineStr">
+      <c r="R34" s="7" t="inlineStr">
         <is>
           <t>理杏仁公开页面</t>
         </is>
@@ -2475,58 +2561,60 @@
         <v>4.58</v>
       </c>
       <c r="D35" s="4" t="n"/>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="F35" s="5" t="n">
+      <c r="H35" s="5" t="n">
         <v>1.7402</v>
       </c>
-      <c r="G35" s="5" t="n">
+      <c r="I35" s="5" t="n">
         <v>2.8398</v>
       </c>
-      <c r="H35" s="6" t="inlineStr">
+      <c r="J35" s="6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J35" s="6" t="inlineStr">
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L35" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K35" s="7" t="inlineStr">
+      <c r="M35" s="7" t="inlineStr">
         <is>
           <t>未进入加大买入区间</t>
         </is>
       </c>
-      <c r="L35" s="3" t="inlineStr">
+      <c r="N35" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="M35" s="4" t="inlineStr">
+      <c r="O35" s="4" t="inlineStr">
         <is>
           <t>4.42</t>
         </is>
       </c>
-      <c r="N35" s="4" t="inlineStr">
+      <c r="P35" s="4" t="inlineStr">
         <is>
           <t>15.75</t>
         </is>
       </c>
-      <c r="O35" s="4" t="inlineStr">
+      <c r="Q35" s="4" t="inlineStr">
         <is>
           <t>6.12</t>
         </is>
       </c>
-      <c r="P35" s="7" t="inlineStr">
+      <c r="R35" s="7" t="inlineStr">
         <is>
           <t>理杏仁公开页面</t>
         </is>
@@ -2547,38 +2635,40 @@
         <v>4.52</v>
       </c>
       <c r="D36" s="4" t="n"/>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="F36" s="5" t="n">
+      <c r="H36" s="5" t="n">
         <v>1.7406</v>
       </c>
-      <c r="G36" s="5" t="n">
+      <c r="I36" s="5" t="n">
         <v>2.7794</v>
       </c>
-      <c r="H36" s="6" t="inlineStr"/>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J36" s="6" t="inlineStr">
+      <c r="J36" s="6" t="inlineStr"/>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L36" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K36" s="7" t="inlineStr">
+      <c r="M36" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L36" s="3" t="n"/>
-      <c r="M36" s="4" t="n"/>
-      <c r="N36" s="4" t="n"/>
+      <c r="N36" s="3" t="n"/>
       <c r="O36" s="4" t="n"/>
-      <c r="P36" s="7" t="inlineStr">
+      <c r="P36" s="4" t="n"/>
+      <c r="Q36" s="4" t="n"/>
+      <c r="R36" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -2599,58 +2689,60 @@
         <v>4.57</v>
       </c>
       <c r="D37" s="4" t="n"/>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="F37" s="5" t="n">
+      <c r="H37" s="5" t="n">
         <v>1.7437</v>
       </c>
-      <c r="G37" s="5" t="n">
+      <c r="I37" s="5" t="n">
         <v>2.8263</v>
       </c>
-      <c r="H37" s="6" t="inlineStr">
+      <c r="J37" s="6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J37" s="6" t="inlineStr">
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L37" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K37" s="7" t="inlineStr">
+      <c r="M37" s="7" t="inlineStr">
         <is>
           <t>未进入加大买入区间</t>
         </is>
       </c>
-      <c r="L37" s="3" t="inlineStr">
+      <c r="N37" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="M37" s="4" t="inlineStr">
+      <c r="O37" s="4" t="inlineStr">
         <is>
           <t>4.45</t>
         </is>
       </c>
-      <c r="N37" s="4" t="inlineStr">
+      <c r="P37" s="4" t="inlineStr">
         <is>
           <t>18.87</t>
         </is>
       </c>
-      <c r="O37" s="4" t="inlineStr">
+      <c r="Q37" s="4" t="inlineStr">
         <is>
           <t>6.12</t>
         </is>
       </c>
-      <c r="P37" s="7" t="inlineStr">
+      <c r="R37" s="7" t="inlineStr">
         <is>
           <t>理杏仁公开页面</t>
         </is>
@@ -2671,58 +2763,60 @@
         <v>4.6</v>
       </c>
       <c r="D38" s="4" t="n"/>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="H38" s="5" t="n">
         <v>1.7404</v>
       </c>
-      <c r="G38" s="5" t="n">
+      <c r="I38" s="5" t="n">
         <v>2.859599999999999</v>
       </c>
-      <c r="H38" s="6" t="inlineStr">
+      <c r="J38" s="6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J38" s="6" t="inlineStr">
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L38" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K38" s="7" t="inlineStr">
+      <c r="M38" s="7" t="inlineStr">
         <is>
           <t>未进入加大买入区间</t>
         </is>
       </c>
-      <c r="L38" s="3" t="inlineStr">
+      <c r="N38" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="M38" s="4" t="inlineStr">
+      <c r="O38" s="4" t="inlineStr">
         <is>
           <t>4.38</t>
         </is>
       </c>
-      <c r="N38" s="4" t="inlineStr">
+      <c r="P38" s="4" t="inlineStr">
         <is>
           <t>12.26</t>
         </is>
       </c>
-      <c r="O38" s="4" t="inlineStr">
+      <c r="Q38" s="4" t="inlineStr">
         <is>
           <t>6.12</t>
         </is>
       </c>
-      <c r="P38" s="7" t="inlineStr">
+      <c r="R38" s="7" t="inlineStr">
         <is>
           <t>理杏仁公开页面</t>
         </is>
@@ -2743,38 +2837,40 @@
         <v>4.46</v>
       </c>
       <c r="D39" s="4" t="n"/>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="F39" s="5" t="n">
+      <c r="H39" s="5" t="n">
         <v>1.7453</v>
       </c>
-      <c r="G39" s="5" t="n">
+      <c r="I39" s="5" t="n">
         <v>2.7147</v>
       </c>
-      <c r="H39" s="6" t="inlineStr"/>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J39" s="6" t="inlineStr">
+      <c r="J39" s="6" t="inlineStr"/>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L39" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K39" s="7" t="inlineStr">
+      <c r="M39" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L39" s="3" t="n"/>
-      <c r="M39" s="4" t="n"/>
-      <c r="N39" s="4" t="n"/>
+      <c r="N39" s="3" t="n"/>
       <c r="O39" s="4" t="n"/>
-      <c r="P39" s="7" t="inlineStr">
+      <c r="P39" s="4" t="n"/>
+      <c r="Q39" s="4" t="n"/>
+      <c r="R39" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -2795,38 +2891,40 @@
         <v>4.46</v>
       </c>
       <c r="D40" s="4" t="n"/>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="F40" s="5" t="n">
+      <c r="H40" s="5" t="n">
         <v>1.7297</v>
       </c>
-      <c r="G40" s="5" t="n">
+      <c r="I40" s="5" t="n">
         <v>2.7303</v>
       </c>
-      <c r="H40" s="6" t="inlineStr"/>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J40" s="6" t="inlineStr">
+      <c r="J40" s="6" t="inlineStr"/>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L40" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K40" s="7" t="inlineStr">
+      <c r="M40" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L40" s="3" t="n"/>
-      <c r="M40" s="4" t="n"/>
-      <c r="N40" s="4" t="n"/>
+      <c r="N40" s="3" t="n"/>
       <c r="O40" s="4" t="n"/>
-      <c r="P40" s="7" t="inlineStr">
+      <c r="P40" s="4" t="n"/>
+      <c r="Q40" s="4" t="n"/>
+      <c r="R40" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -2847,58 +2945,60 @@
         <v>4.41</v>
       </c>
       <c r="D41" s="4" t="n"/>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="F41" s="5" t="n">
+      <c r="H41" s="5" t="n">
         <v>1.7325</v>
       </c>
-      <c r="G41" s="5" t="n">
+      <c r="I41" s="5" t="n">
         <v>2.6775</v>
       </c>
-      <c r="H41" s="6" t="inlineStr">
+      <c r="J41" s="6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J41" s="6" t="inlineStr">
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L41" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K41" s="7" t="inlineStr">
+      <c r="M41" s="7" t="inlineStr">
         <is>
           <t>未进入加大买入区间</t>
         </is>
       </c>
-      <c r="L41" s="3" t="inlineStr">
+      <c r="N41" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="M41" s="4" t="inlineStr">
+      <c r="O41" s="4" t="inlineStr">
         <is>
           <t>4.23</t>
         </is>
       </c>
-      <c r="N41" s="4" t="inlineStr">
+      <c r="P41" s="4" t="inlineStr">
         <is>
           <t>4.96</t>
         </is>
       </c>
-      <c r="O41" s="4" t="inlineStr">
+      <c r="Q41" s="4" t="inlineStr">
         <is>
           <t>6.12</t>
         </is>
       </c>
-      <c r="P41" s="7" t="inlineStr">
+      <c r="R41" s="7" t="inlineStr">
         <is>
           <t>理杏仁公开页面</t>
         </is>
@@ -2919,38 +3019,40 @@
         <v>4.5</v>
       </c>
       <c r="D42" s="4" t="n"/>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="F42" s="5" t="n">
+      <c r="H42" s="5" t="n">
         <v>1.7282</v>
       </c>
-      <c r="G42" s="5" t="n">
+      <c r="I42" s="5" t="n">
         <v>2.7718</v>
       </c>
-      <c r="H42" s="6" t="inlineStr"/>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J42" s="6" t="inlineStr">
+      <c r="J42" s="6" t="inlineStr"/>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L42" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K42" s="7" t="inlineStr">
+      <c r="M42" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L42" s="3" t="n"/>
-      <c r="M42" s="4" t="n"/>
-      <c r="N42" s="4" t="n"/>
+      <c r="N42" s="3" t="n"/>
       <c r="O42" s="4" t="n"/>
-      <c r="P42" s="7" t="inlineStr">
+      <c r="P42" s="4" t="n"/>
+      <c r="Q42" s="4" t="n"/>
+      <c r="R42" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -2971,38 +3073,40 @@
         <v>4.47</v>
       </c>
       <c r="D43" s="4" t="n"/>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="F43" s="5" t="n">
+      <c r="H43" s="5" t="n">
         <v>1.7337</v>
       </c>
-      <c r="G43" s="5" t="n">
+      <c r="I43" s="5" t="n">
         <v>2.7363</v>
       </c>
-      <c r="H43" s="6" t="inlineStr"/>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J43" s="6" t="inlineStr">
+      <c r="J43" s="6" t="inlineStr"/>
+      <c r="K43" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L43" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K43" s="7" t="inlineStr">
+      <c r="M43" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L43" s="3" t="n"/>
-      <c r="M43" s="4" t="n"/>
-      <c r="N43" s="4" t="n"/>
+      <c r="N43" s="3" t="n"/>
       <c r="O43" s="4" t="n"/>
-      <c r="P43" s="7" t="inlineStr">
+      <c r="P43" s="4" t="n"/>
+      <c r="Q43" s="4" t="n"/>
+      <c r="R43" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -3023,58 +3127,60 @@
         <v>4.47</v>
       </c>
       <c r="D44" s="4" t="n"/>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="3" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="F44" s="5" t="n">
+      <c r="H44" s="5" t="n">
         <v>1.7351</v>
       </c>
-      <c r="G44" s="5" t="n">
+      <c r="I44" s="5" t="n">
         <v>2.7349</v>
       </c>
-      <c r="H44" s="6" t="inlineStr">
+      <c r="J44" s="6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J44" s="6" t="inlineStr">
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L44" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K44" s="7" t="inlineStr">
+      <c r="M44" s="7" t="inlineStr">
         <is>
           <t>未进入加大买入区间</t>
         </is>
       </c>
-      <c r="L44" s="3" t="inlineStr">
+      <c r="N44" s="3" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="M44" s="4" t="inlineStr">
+      <c r="O44" s="4" t="inlineStr">
         <is>
           <t>4.18</t>
         </is>
       </c>
-      <c r="N44" s="4" t="inlineStr">
+      <c r="P44" s="4" t="inlineStr">
         <is>
           <t>2.34</t>
         </is>
       </c>
-      <c r="O44" s="4" t="inlineStr">
+      <c r="Q44" s="4" t="inlineStr">
         <is>
           <t>6.11</t>
         </is>
       </c>
-      <c r="P44" s="7" t="inlineStr">
+      <c r="R44" s="7" t="inlineStr">
         <is>
           <t>理杏仁公开页面</t>
         </is>
@@ -3095,58 +3201,60 @@
         <v>4.4</v>
       </c>
       <c r="D45" s="4" t="n"/>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="F45" s="5" t="n">
+      <c r="H45" s="5" t="n">
         <v>1.7329</v>
       </c>
-      <c r="G45" s="5" t="n">
+      <c r="I45" s="5" t="n">
         <v>2.6671</v>
       </c>
-      <c r="H45" s="6" t="inlineStr">
+      <c r="J45" s="6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J45" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="inlineStr">
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L45" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M45" s="7" t="inlineStr">
         <is>
           <t>未进入加大买入区间</t>
         </is>
       </c>
-      <c r="L45" s="3" t="inlineStr">
+      <c r="N45" s="3" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="M45" s="4" t="inlineStr">
+      <c r="O45" s="4" t="inlineStr">
         <is>
           <t>4.18</t>
         </is>
       </c>
-      <c r="N45" s="4" t="inlineStr">
+      <c r="P45" s="4" t="inlineStr">
         <is>
           <t>2.34</t>
         </is>
       </c>
-      <c r="O45" s="4" t="inlineStr">
+      <c r="Q45" s="4" t="inlineStr">
         <is>
           <t>6.11</t>
         </is>
       </c>
-      <c r="P45" s="7" t="inlineStr">
+      <c r="R45" s="7" t="inlineStr">
         <is>
           <t>理杏仁公开页面</t>
         </is>
@@ -3167,58 +3275,60 @@
         <v>4.36</v>
       </c>
       <c r="D46" s="4" t="n"/>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="3" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="F46" s="5" t="n">
+      <c r="H46" s="5" t="n">
         <v>1.7196</v>
       </c>
-      <c r="G46" s="5" t="n">
+      <c r="I46" s="5" t="n">
         <v>2.640400000000001</v>
       </c>
-      <c r="H46" s="6" t="inlineStr">
+      <c r="J46" s="6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J46" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="inlineStr">
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L46" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M46" s="7" t="inlineStr">
         <is>
           <t>未进入加大买入区间</t>
         </is>
       </c>
-      <c r="L46" s="3" t="inlineStr">
+      <c r="N46" s="3" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="M46" s="4" t="inlineStr">
+      <c r="O46" s="4" t="inlineStr">
         <is>
           <t>4.08</t>
         </is>
       </c>
-      <c r="N46" s="4" t="inlineStr">
+      <c r="P46" s="4" t="inlineStr">
         <is>
           <t>0.14</t>
         </is>
       </c>
-      <c r="O46" s="4" t="inlineStr">
+      <c r="Q46" s="4" t="inlineStr">
         <is>
           <t>6.11</t>
         </is>
       </c>
-      <c r="P46" s="7" t="inlineStr">
+      <c r="R46" s="7" t="inlineStr">
         <is>
           <t>理杏仁公开页面</t>
         </is>
@@ -3239,38 +3349,40 @@
         <v>4.15</v>
       </c>
       <c r="D47" s="4" t="n"/>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="4" t="n"/>
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="F47" s="5" t="n">
+      <c r="H47" s="5" t="n">
         <v>1.7141</v>
       </c>
-      <c r="G47" s="5" t="n">
+      <c r="I47" s="5" t="n">
         <v>2.4359</v>
       </c>
-      <c r="H47" s="6" t="inlineStr"/>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J47" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="inlineStr">
+      <c r="J47" s="6" t="inlineStr"/>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L47" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M47" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L47" s="3" t="n"/>
-      <c r="M47" s="4" t="n"/>
-      <c r="N47" s="4" t="n"/>
+      <c r="N47" s="3" t="n"/>
       <c r="O47" s="4" t="n"/>
-      <c r="P47" s="7" t="inlineStr">
+      <c r="P47" s="4" t="n"/>
+      <c r="Q47" s="4" t="n"/>
+      <c r="R47" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -3291,38 +3403,40 @@
         <v>4.16</v>
       </c>
       <c r="D48" s="4" t="n"/>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="n"/>
+      <c r="G48" s="3" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F48" s="5" t="n">
+      <c r="H48" s="5" t="n">
         <v>1.7169</v>
       </c>
-      <c r="G48" s="5" t="n">
+      <c r="I48" s="5" t="n">
         <v>2.4431</v>
       </c>
-      <c r="H48" s="6" t="inlineStr"/>
-      <c r="I48" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J48" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="inlineStr">
+      <c r="J48" s="6" t="inlineStr"/>
+      <c r="K48" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L48" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M48" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L48" s="3" t="n"/>
-      <c r="M48" s="4" t="n"/>
-      <c r="N48" s="4" t="n"/>
+      <c r="N48" s="3" t="n"/>
       <c r="O48" s="4" t="n"/>
-      <c r="P48" s="7" t="inlineStr">
+      <c r="P48" s="4" t="n"/>
+      <c r="Q48" s="4" t="n"/>
+      <c r="R48" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -3343,58 +3457,60 @@
         <v>4.23</v>
       </c>
       <c r="D49" s="4" t="n"/>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="4" t="n"/>
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F49" s="5" t="n">
+      <c r="H49" s="5" t="n">
         <v>1.7126</v>
       </c>
-      <c r="G49" s="5" t="n">
+      <c r="I49" s="5" t="n">
         <v>2.5174</v>
       </c>
-      <c r="H49" s="6" t="inlineStr">
+      <c r="J49" s="6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J49" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="inlineStr">
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L49" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M49" s="7" t="inlineStr">
         <is>
           <t>未进入加大买入区间</t>
         </is>
       </c>
-      <c r="L49" s="3" t="inlineStr">
+      <c r="N49" s="3" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="M49" s="4" t="inlineStr">
+      <c r="O49" s="4" t="inlineStr">
         <is>
           <t>4.28</t>
         </is>
       </c>
-      <c r="N49" s="4" t="inlineStr">
+      <c r="P49" s="4" t="inlineStr">
         <is>
           <t>7.87</t>
         </is>
       </c>
-      <c r="O49" s="4" t="inlineStr">
+      <c r="Q49" s="4" t="inlineStr">
         <is>
           <t>6.11</t>
         </is>
       </c>
-      <c r="P49" s="7" t="inlineStr">
+      <c r="R49" s="7" t="inlineStr">
         <is>
           <t>理杏仁公开页面</t>
         </is>
@@ -3415,58 +3531,60 @@
         <v>4.24</v>
       </c>
       <c r="D50" s="4" t="n"/>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E50" s="4" t="n"/>
+      <c r="F50" s="4" t="n"/>
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F50" s="5" t="n">
+      <c r="H50" s="5" t="n">
         <v>1.7137</v>
       </c>
-      <c r="G50" s="5" t="n">
+      <c r="I50" s="5" t="n">
         <v>2.5263</v>
       </c>
-      <c r="H50" s="6" t="inlineStr">
+      <c r="J50" s="6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J50" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K50" s="7" t="inlineStr">
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L50" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M50" s="7" t="inlineStr">
         <is>
           <t>未进入加大买入区间</t>
         </is>
       </c>
-      <c r="L50" s="3" t="inlineStr">
+      <c r="N50" s="3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="M50" s="4" t="inlineStr">
+      <c r="O50" s="4" t="inlineStr">
         <is>
           <t>4.34</t>
         </is>
       </c>
-      <c r="N50" s="4" t="inlineStr">
+      <c r="P50" s="4" t="inlineStr">
         <is>
           <t>10.34</t>
         </is>
       </c>
-      <c r="O50" s="4" t="inlineStr">
+      <c r="Q50" s="4" t="inlineStr">
         <is>
           <t>6.11</t>
         </is>
       </c>
-      <c r="P50" s="7" t="inlineStr">
+      <c r="R50" s="7" t="inlineStr">
         <is>
           <t>理杏仁公开页面</t>
         </is>
@@ -3487,38 +3605,40 @@
         <v>4.19</v>
       </c>
       <c r="D51" s="4" t="n"/>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="n"/>
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="F51" s="5" t="n">
+      <c r="H51" s="5" t="n">
         <v>1.7143</v>
       </c>
-      <c r="G51" s="5" t="n">
+      <c r="I51" s="5" t="n">
         <v>2.475700000000001</v>
       </c>
-      <c r="H51" s="6" t="inlineStr"/>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J51" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="inlineStr">
+      <c r="J51" s="6" t="inlineStr"/>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L51" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M51" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L51" s="3" t="n"/>
-      <c r="M51" s="4" t="n"/>
-      <c r="N51" s="4" t="n"/>
+      <c r="N51" s="3" t="n"/>
       <c r="O51" s="4" t="n"/>
-      <c r="P51" s="7" t="inlineStr">
+      <c r="P51" s="4" t="n"/>
+      <c r="Q51" s="4" t="n"/>
+      <c r="R51" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -3539,38 +3659,40 @@
         <v>4.2</v>
       </c>
       <c r="D52" s="4" t="n"/>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="n"/>
+      <c r="G52" s="3" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="F52" s="5" t="n">
+      <c r="H52" s="5" t="n">
         <v>1.7114</v>
       </c>
-      <c r="G52" s="5" t="n">
+      <c r="I52" s="5" t="n">
         <v>2.4886</v>
       </c>
-      <c r="H52" s="6" t="inlineStr"/>
-      <c r="I52" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J52" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="inlineStr">
+      <c r="J52" s="6" t="inlineStr"/>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L52" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M52" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L52" s="3" t="n"/>
-      <c r="M52" s="4" t="n"/>
-      <c r="N52" s="4" t="n"/>
+      <c r="N52" s="3" t="n"/>
       <c r="O52" s="4" t="n"/>
-      <c r="P52" s="7" t="inlineStr">
+      <c r="P52" s="4" t="n"/>
+      <c r="Q52" s="4" t="n"/>
+      <c r="R52" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -3591,38 +3713,40 @@
         <v>4.16</v>
       </c>
       <c r="D53" s="4" t="n"/>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="n"/>
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="F53" s="5" t="n">
+      <c r="H53" s="5" t="n">
         <v>1.7074</v>
       </c>
-      <c r="G53" s="5" t="n">
+      <c r="I53" s="5" t="n">
         <v>2.4526</v>
       </c>
-      <c r="H53" s="6" t="inlineStr"/>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J53" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="inlineStr">
+      <c r="J53" s="6" t="inlineStr"/>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L53" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M53" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L53" s="3" t="n"/>
-      <c r="M53" s="4" t="n"/>
-      <c r="N53" s="4" t="n"/>
+      <c r="N53" s="3" t="n"/>
       <c r="O53" s="4" t="n"/>
-      <c r="P53" s="7" t="inlineStr">
+      <c r="P53" s="4" t="n"/>
+      <c r="Q53" s="4" t="n"/>
+      <c r="R53" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -3643,58 +3767,60 @@
         <v>4.18</v>
       </c>
       <c r="D54" s="4" t="n"/>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E54" s="4" t="n"/>
+      <c r="F54" s="4" t="n"/>
+      <c r="G54" s="3" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F54" s="5" t="n">
+      <c r="H54" s="5" t="n">
         <v>1.7161</v>
       </c>
-      <c r="G54" s="5" t="n">
+      <c r="I54" s="5" t="n">
         <v>2.4639</v>
       </c>
-      <c r="H54" s="6" t="inlineStr">
+      <c r="J54" s="6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J54" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K54" s="7" t="inlineStr">
+      <c r="K54" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L54" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M54" s="7" t="inlineStr">
         <is>
           <t>未进入加大买入区间</t>
         </is>
       </c>
-      <c r="L54" s="3" t="inlineStr">
+      <c r="N54" s="3" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="M54" s="4" t="inlineStr">
+      <c r="O54" s="4" t="inlineStr">
         <is>
           <t>4.26</t>
         </is>
       </c>
-      <c r="N54" s="4" t="inlineStr">
+      <c r="P54" s="4" t="inlineStr">
         <is>
           <t>7.04</t>
         </is>
       </c>
-      <c r="O54" s="4" t="inlineStr">
+      <c r="Q54" s="4" t="inlineStr">
         <is>
           <t>6.11</t>
         </is>
       </c>
-      <c r="P54" s="7" t="inlineStr">
+      <c r="R54" s="7" t="inlineStr">
         <is>
           <t>理杏仁公开页面</t>
         </is>
@@ -3715,38 +3841,40 @@
         <v>4.19</v>
       </c>
       <c r="D55" s="4" t="n"/>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E55" s="4" t="n"/>
+      <c r="F55" s="4" t="n"/>
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F55" s="5" t="n">
+      <c r="H55" s="5" t="n">
         <v>1.7141</v>
       </c>
-      <c r="G55" s="5" t="n">
+      <c r="I55" s="5" t="n">
         <v>2.4759</v>
       </c>
-      <c r="H55" s="6" t="inlineStr"/>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J55" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K55" s="7" t="inlineStr">
+      <c r="J55" s="6" t="inlineStr"/>
+      <c r="K55" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L55" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M55" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L55" s="3" t="n"/>
-      <c r="M55" s="4" t="n"/>
-      <c r="N55" s="4" t="n"/>
+      <c r="N55" s="3" t="n"/>
       <c r="O55" s="4" t="n"/>
-      <c r="P55" s="7" t="inlineStr">
+      <c r="P55" s="4" t="n"/>
+      <c r="Q55" s="4" t="n"/>
+      <c r="R55" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -3767,38 +3895,40 @@
         <v>4.23</v>
       </c>
       <c r="D56" s="4" t="n"/>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E56" s="4" t="n"/>
+      <c r="F56" s="4" t="n"/>
+      <c r="G56" s="3" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="F56" s="5" t="n">
+      <c r="H56" s="5" t="n">
         <v>1.7032</v>
       </c>
-      <c r="G56" s="5" t="n">
+      <c r="I56" s="5" t="n">
         <v>2.526800000000001</v>
       </c>
-      <c r="H56" s="6" t="inlineStr"/>
-      <c r="I56" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J56" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K56" s="7" t="inlineStr">
+      <c r="J56" s="6" t="inlineStr"/>
+      <c r="K56" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L56" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M56" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L56" s="3" t="n"/>
-      <c r="M56" s="4" t="n"/>
-      <c r="N56" s="4" t="n"/>
+      <c r="N56" s="3" t="n"/>
       <c r="O56" s="4" t="n"/>
-      <c r="P56" s="7" t="inlineStr">
+      <c r="P56" s="4" t="n"/>
+      <c r="Q56" s="4" t="n"/>
+      <c r="R56" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -3819,58 +3949,60 @@
         <v>4.22</v>
       </c>
       <c r="D57" s="4" t="n"/>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E57" s="4" t="n"/>
+      <c r="F57" s="4" t="n"/>
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="F57" s="5" t="n">
+      <c r="H57" s="5" t="n">
         <v>1.6964</v>
       </c>
-      <c r="G57" s="5" t="n">
+      <c r="I57" s="5" t="n">
         <v>2.5236</v>
       </c>
-      <c r="H57" s="6" t="inlineStr">
+      <c r="J57" s="6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J57" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K57" s="7" t="inlineStr">
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L57" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M57" s="7" t="inlineStr">
         <is>
           <t>未进入加大买入区间</t>
         </is>
       </c>
-      <c r="L57" s="3" t="inlineStr">
+      <c r="N57" s="3" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="M57" s="4" t="inlineStr">
+      <c r="O57" s="4" t="inlineStr">
         <is>
           <t>4.30</t>
         </is>
       </c>
-      <c r="N57" s="4" t="inlineStr">
+      <c r="P57" s="4" t="inlineStr">
         <is>
           <t>8.95</t>
         </is>
       </c>
-      <c r="O57" s="4" t="inlineStr">
+      <c r="Q57" s="4" t="inlineStr">
         <is>
           <t>6.11</t>
         </is>
       </c>
-      <c r="P57" s="7" t="inlineStr">
+      <c r="R57" s="7" t="inlineStr">
         <is>
           <t>理杏仁公开页面</t>
         </is>
@@ -3891,38 +4023,40 @@
         <v>4.2</v>
       </c>
       <c r="D58" s="4" t="n"/>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E58" s="4" t="n"/>
+      <c r="F58" s="4" t="n"/>
+      <c r="G58" s="3" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="F58" s="5" t="n">
+      <c r="H58" s="5" t="n">
         <v>1.6924</v>
       </c>
-      <c r="G58" s="5" t="n">
+      <c r="I58" s="5" t="n">
         <v>2.5076</v>
       </c>
-      <c r="H58" s="6" t="inlineStr"/>
-      <c r="I58" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J58" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K58" s="7" t="inlineStr">
+      <c r="J58" s="6" t="inlineStr"/>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L58" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M58" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L58" s="3" t="n"/>
-      <c r="M58" s="4" t="n"/>
-      <c r="N58" s="4" t="n"/>
+      <c r="N58" s="3" t="n"/>
       <c r="O58" s="4" t="n"/>
-      <c r="P58" s="7" t="inlineStr">
+      <c r="P58" s="4" t="n"/>
+      <c r="Q58" s="4" t="n"/>
+      <c r="R58" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
@@ -3942,46 +4076,164 @@
       <c r="C59" s="4" t="n">
         <v>4.17</v>
       </c>
-      <c r="D59" s="4" t="inlineStr"/>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="D59" s="4" t="n"/>
+      <c r="E59" s="4" t="n"/>
+      <c r="F59" s="4" t="n"/>
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="F59" s="5" t="n">
+      <c r="H59" s="5" t="n">
         <v>1.6864</v>
       </c>
-      <c r="G59" s="5" t="n">
+      <c r="I59" s="5" t="n">
         <v>2.4836</v>
       </c>
-      <c r="H59" s="6" t="inlineStr"/>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J59" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K59" s="7" t="inlineStr">
+      <c r="J59" s="6" t="inlineStr"/>
+      <c r="K59" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L59" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M59" s="7" t="inlineStr">
         <is>
           <t>历史分位点待验证，暂不判定加大买入区间</t>
         </is>
       </c>
-      <c r="L59" s="3" t="inlineStr"/>
-      <c r="M59" s="4" t="inlineStr"/>
-      <c r="N59" s="4" t="inlineStr"/>
-      <c r="O59" s="4" t="inlineStr"/>
-      <c r="P59" s="7" t="inlineStr">
+      <c r="N59" s="3" t="n"/>
+      <c r="O59" s="4" t="n"/>
+      <c r="P59" s="4" t="n"/>
+      <c r="Q59" s="4" t="n"/>
+      <c r="R59" s="7" t="inlineStr">
         <is>
           <t>理杏仁待验证</t>
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>0.5105771458357555</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F60" s="4" t="n"/>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>1.6831</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>2.4769</v>
+      </c>
+      <c r="J60" s="6" t="inlineStr"/>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L60" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M60" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="n"/>
+      <c r="O60" s="4" t="n"/>
+      <c r="P60" s="4" t="n"/>
+      <c r="Q60" s="4" t="n"/>
+      <c r="R60" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>1.085587281362232</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>-15.96361099166238</v>
+      </c>
+      <c r="F61" s="4" t="inlineStr"/>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>1.6832</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>2.456799999999999</v>
+      </c>
+      <c r="J61" s="6" t="inlineStr"/>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L61" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M61" s="7" t="inlineStr">
+        <is>
+          <t>历史分位点待验证，暂不判定加大买入区间</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr"/>
+      <c r="O61" s="4" t="inlineStr"/>
+      <c r="P61" s="4" t="inlineStr"/>
+      <c r="Q61" s="4" t="inlineStr"/>
+      <c r="R61" s="7" t="inlineStr">
+        <is>
+          <t>理杏仁待验证</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P59"/>
+  <autoFilter ref="A1:R61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>